--- a/base_control_efectivo.xlsx
+++ b/base_control_efectivo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Otros ordenadores\Mi portátil\Desktop\Conciliacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBBCA162-AF8A-4D6C-A8D3-7E08A920D427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A88F22-2D3B-4026-B605-5EC0734B8438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5A6B522A-9DEE-4D44-863C-DA3950676BAE}"/>
   </bookViews>
